--- a/static/uploads/ProgramariE2-20260727.xlsx
+++ b/static/uploads/ProgramariE2-20260727.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frank\Desktop\master_2026_local\pv_comisii_etapa2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\UPT\admitere master\admissions-ac\static\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D426306E-73A8-4721-AC3F-EC6AB96122B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1741813-4AF5-42A4-A5C2-C29B293E02E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{522CC8CF-E1EA-CE4F-B203-B694DA3F9D23}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{522CC8CF-E1EA-CE4F-B203-B694DA3F9D23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -50,9 +50,6 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Comisie</t>
-  </si>
-  <si>
     <t>Luni, 27 Iulie</t>
   </si>
   <si>
@@ -114,9 +111,12 @@
   </si>
   <si>
     <t>Topic: Masters admissions
-Time: Jul 27, 2026 08:00 AM Bucharest
+Time: 27 July 2026 09:00 AM Bucharest
 Link:
 https://teams.microsoft.com/meet/382085888270755?p=p8X4KUTogZDvobGWWw</t>
+  </si>
+  <si>
+    <t>Comisia E2</t>
   </si>
 </sst>
 </file>
@@ -540,7 +540,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -561,13 +561,13 @@
         <v>0.375</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>5</v>
-      </c>
       <c r="D3" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
@@ -583,10 +583,10 @@
         <v>0.37916666666666665</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -603,10 +603,10 @@
         <v>0.3833333333333333</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -623,10 +623,10 @@
         <v>0.38749999999999996</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -643,10 +643,10 @@
         <v>0.39166666666666661</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -663,10 +663,10 @@
         <v>0.39583333333333326</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -683,10 +683,10 @@
         <v>0.39999999999999991</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -703,10 +703,10 @@
         <v>0.40416666666666656</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
@@ -723,10 +723,10 @@
         <v>0.40833333333333321</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -743,10 +743,10 @@
         <v>0.41249999999999987</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -763,10 +763,10 @@
         <v>0.41666666666666652</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -783,10 +783,10 @@
         <v>0.42083333333333317</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -803,10 +803,10 @@
         <v>0.42499999999999982</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -823,10 +823,10 @@
         <v>0.42916666666666647</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -843,10 +843,10 @@
         <v>0.43333333333333313</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -863,10 +863,10 @@
         <v>0.43749999999999978</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
@@ -883,10 +883,10 @@
         <v>0.44166666666666643</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -903,10 +903,10 @@
         <v>0.44583333333333308</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -923,10 +923,10 @@
         <v>0.44999999999999973</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
